--- a/Orçado/Orça-Pecuária/COVOA - PECUÁRIA.xlsx
+++ b/Orçado/Orça-Pecuária/COVOA - PECUÁRIA.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\henrique.santos\orcamento2027\budgetflow-insights\Orçado\Orça-Pecuária\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14C8B83F-1E14-4973-8A37-149F969F5FB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95A55CA7-3762-4B0C-95D9-926AC19E5331}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{249BD8F4-57E6-4DA0-9D36-EDD8CCD9DE40}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="38">
   <si>
     <t>Descrição C. Contábil</t>
   </si>
@@ -150,6 +150,12 @@
   </si>
   <si>
     <t>4.1.01.01-CUSTO DE PESSOAL</t>
+  </si>
+  <si>
+    <t>4.1.01.04.0003</t>
+  </si>
+  <si>
+    <t>MATERIAIS PARA MANUTENCAO E REFORMA</t>
   </si>
 </sst>
 </file>
@@ -160,7 +166,7 @@
     <numFmt numFmtId="44" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="&quot;R$&quot;\ #,##0.00"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -189,6 +195,12 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -210,7 +222,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -257,13 +269,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -277,13 +300,27 @@
     <xf numFmtId="17" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="4" fillId="3" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="4" fillId="3" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Moeda 2" xfId="2" xr:uid="{0EE902CF-FB87-4B69-87FA-F22B0CAC8E45}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{6B059D2C-A075-4C9D-9188-7FCECE08C195}"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -586,12 +623,12 @@
   <sheetPr>
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
-  <dimension ref="A1:P15"/>
+  <dimension ref="A1:P16"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="50.21875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16.21875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="30.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="40.33203125" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="8" width="13.6640625" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="12.6640625" style="1" bestFit="1" customWidth="1"/>
     <col min="10" max="15" width="13.6640625" style="1" bestFit="1" customWidth="1"/>
@@ -671,7 +708,8 @@
         <v>58035.809700000013</v>
       </c>
       <c r="J2" s="6">
-        <v>45453.424500000008</v>
+        <f>45453.4245+3000</f>
+        <v>48453.424500000001</v>
       </c>
       <c r="K2" s="6">
         <v>5540.3705499999996</v>
@@ -691,175 +729,175 @@
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3" s="5">
-        <v>1051.08761175</v>
-      </c>
-      <c r="E3" s="6">
-        <v>1051.08761175</v>
-      </c>
-      <c r="F3" s="6">
-        <v>1109.5135432500001</v>
-      </c>
-      <c r="G3" s="6">
-        <v>1109.5135432500001</v>
-      </c>
-      <c r="H3" s="6">
-        <v>998.5621889250001</v>
-      </c>
-      <c r="I3" s="6">
-        <v>998.5621889250001</v>
-      </c>
-      <c r="J3" s="6">
-        <v>942.98823540000001</v>
-      </c>
-      <c r="K3" s="6">
-        <v>942.98823540000001</v>
-      </c>
-      <c r="L3" s="6">
-        <v>981.61200000000008</v>
-      </c>
-      <c r="M3" s="6">
-        <v>981.61200000000008</v>
-      </c>
-      <c r="N3" s="7">
-        <v>981.61200000000008</v>
-      </c>
-      <c r="O3" s="7">
-        <v>981.61200000000008</v>
+        <v>36</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="D3" s="10">
+        <v>0</v>
+      </c>
+      <c r="E3" s="11">
+        <v>0</v>
+      </c>
+      <c r="F3" s="11">
+        <v>0</v>
+      </c>
+      <c r="G3" s="11">
+        <v>0</v>
+      </c>
+      <c r="H3" s="11">
+        <v>0</v>
+      </c>
+      <c r="I3" s="11">
+        <v>0</v>
+      </c>
+      <c r="J3" s="11">
+        <v>10833.33</v>
+      </c>
+      <c r="K3" s="11">
+        <v>0</v>
+      </c>
+      <c r="L3" s="11">
+        <v>0</v>
+      </c>
+      <c r="M3" s="11">
+        <v>0</v>
+      </c>
+      <c r="N3" s="11">
+        <v>0</v>
+      </c>
+      <c r="O3" s="11">
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D4" s="5">
-        <v>652.02774999999997</v>
+        <v>1051.08761175</v>
       </c>
       <c r="E4" s="6">
-        <v>856.33570000000009</v>
+        <v>1051.08761175</v>
       </c>
       <c r="F4" s="6">
-        <v>938.08605000000011</v>
+        <v>1109.5135432500001</v>
       </c>
       <c r="G4" s="6">
-        <v>981.77750000000015</v>
+        <v>1109.5135432500001</v>
       </c>
       <c r="H4" s="6">
-        <v>974.8596</v>
+        <v>998.5621889250001</v>
       </c>
       <c r="I4" s="6">
-        <v>968.45375000000013</v>
+        <v>998.5621889250001</v>
       </c>
       <c r="J4" s="6">
-        <v>1081.9616500000006</v>
+        <v>942.98823540000001</v>
       </c>
       <c r="K4" s="6">
-        <v>1081.9616500000006</v>
+        <v>942.98823540000001</v>
       </c>
       <c r="L4" s="6">
-        <v>1081.9616500000006</v>
+        <v>981.61200000000008</v>
       </c>
       <c r="M4" s="6">
-        <v>652.02774999999997</v>
+        <v>981.61200000000008</v>
       </c>
       <c r="N4" s="7">
-        <v>652.02774999999997</v>
+        <v>981.61200000000008</v>
       </c>
       <c r="O4" s="7">
-        <v>652.43529999999987</v>
+        <v>981.61200000000008</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B5" t="s">
-        <v>17</v>
+        <v>28</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>16</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D5" s="5">
-        <v>0</v>
+        <v>652.02774999999997</v>
       </c>
       <c r="E5" s="6">
-        <v>5026.7217000000001</v>
+        <v>856.33570000000009</v>
       </c>
       <c r="F5" s="6">
-        <v>0</v>
+        <v>938.08605000000011</v>
       </c>
       <c r="G5" s="6">
-        <v>0</v>
+        <v>981.77750000000015</v>
       </c>
       <c r="H5" s="6">
-        <v>0</v>
+        <v>974.8596</v>
       </c>
       <c r="I5" s="6">
-        <v>0</v>
+        <v>968.45375000000013</v>
       </c>
       <c r="J5" s="6">
-        <v>4407.8727000000008</v>
+        <v>1081.9616500000006</v>
       </c>
       <c r="K5" s="6">
-        <v>0</v>
+        <v>1081.9616500000006</v>
       </c>
       <c r="L5" s="6">
-        <v>0</v>
+        <v>1081.9616500000006</v>
       </c>
       <c r="M5" s="6">
-        <v>0</v>
+        <v>652.02774999999997</v>
       </c>
       <c r="N5" s="7">
-        <v>0</v>
+        <v>652.02774999999997</v>
       </c>
       <c r="O5" s="7">
-        <v>0</v>
+        <v>652.43529999999987</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>18</v>
+        <v>29</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D6" s="5">
         <v>0</v>
       </c>
       <c r="E6" s="6">
-        <v>0</v>
+        <v>5026.7217000000001</v>
       </c>
       <c r="F6" s="6">
         <v>0</v>
       </c>
       <c r="G6" s="6">
-        <v>106.19290000000001</v>
+        <v>0</v>
       </c>
       <c r="H6" s="6">
-        <v>2090</v>
+        <v>0</v>
       </c>
       <c r="I6" s="6">
         <v>0</v>
       </c>
       <c r="J6" s="6">
-        <v>0</v>
+        <v>4407.8727000000008</v>
       </c>
       <c r="K6" s="6">
         <v>0</v>
@@ -868,7 +906,7 @@
         <v>0</v>
       </c>
       <c r="M6" s="6">
-        <v>2098.0673999999999</v>
+        <v>0</v>
       </c>
       <c r="N6" s="7">
         <v>0</v>
@@ -879,115 +917,114 @@
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D7" s="5">
+        <v>0</v>
+      </c>
+      <c r="E7" s="6">
+        <v>0</v>
+      </c>
+      <c r="F7" s="6">
+        <v>0</v>
+      </c>
+      <c r="G7" s="6">
+        <v>106.19290000000001</v>
+      </c>
+      <c r="H7" s="6">
+        <v>2090</v>
+      </c>
+      <c r="I7" s="6">
+        <v>0</v>
+      </c>
+      <c r="J7" s="6">
+        <v>0</v>
+      </c>
+      <c r="K7" s="6">
+        <v>0</v>
+      </c>
+      <c r="L7" s="6">
+        <v>0</v>
+      </c>
+      <c r="M7" s="6">
+        <v>2098.0673999999999</v>
+      </c>
+      <c r="N7" s="7">
+        <v>0</v>
+      </c>
+      <c r="O7" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B8" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C8" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="5">
-        <v>0</v>
-      </c>
-      <c r="E7" s="6">
+      <c r="D8" s="5">
+        <v>0</v>
+      </c>
+      <c r="E8" s="6">
         <v>1614.2219500000001</v>
       </c>
-      <c r="F7" s="6">
-        <v>0</v>
-      </c>
-      <c r="G7" s="6">
-        <v>0</v>
-      </c>
-      <c r="H7" s="6">
-        <v>0</v>
-      </c>
-      <c r="I7" s="6">
-        <v>0</v>
-      </c>
-      <c r="J7" s="6">
+      <c r="F8" s="6">
+        <v>0</v>
+      </c>
+      <c r="G8" s="6">
+        <v>0</v>
+      </c>
+      <c r="H8" s="6">
+        <v>0</v>
+      </c>
+      <c r="I8" s="6">
+        <v>0</v>
+      </c>
+      <c r="J8" s="6">
         <v>853.3261</v>
       </c>
-      <c r="K7" s="6">
-        <v>0</v>
-      </c>
-      <c r="L7" s="6">
-        <v>0</v>
-      </c>
-      <c r="M7" s="6">
-        <v>0</v>
-      </c>
-      <c r="N7" s="7">
-        <v>0</v>
-      </c>
-      <c r="O7" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
+      <c r="K8" s="6">
+        <v>0</v>
+      </c>
+      <c r="L8" s="6">
+        <v>0</v>
+      </c>
+      <c r="M8" s="6">
+        <v>0</v>
+      </c>
+      <c r="N8" s="7">
+        <v>0</v>
+      </c>
+      <c r="O8" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
         <v>35</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C9" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D8" s="6">
-        <v>0</v>
-      </c>
-      <c r="E8" s="6">
+      <c r="D9" s="6">
+        <v>0</v>
+      </c>
+      <c r="E9" s="6">
         <v>222.59545</v>
       </c>
-      <c r="F8" s="6">
+      <c r="F9" s="6">
         <v>2199.4114999999997</v>
       </c>
-      <c r="G8" s="6">
-        <v>0</v>
-      </c>
-      <c r="H8" s="6">
-        <v>0</v>
-      </c>
-      <c r="I8" s="6">
-        <v>0</v>
-      </c>
-      <c r="J8" s="6">
-        <v>0</v>
-      </c>
-      <c r="K8" s="6">
-        <v>0</v>
-      </c>
-      <c r="L8" s="6">
-        <v>0</v>
-      </c>
-      <c r="M8" s="6">
-        <v>0</v>
-      </c>
-      <c r="N8" s="6">
-        <v>0</v>
-      </c>
-      <c r="O8" s="6">
-        <v>0</v>
-      </c>
-      <c r="P8" s="4"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A9" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D9" s="5">
-        <v>0</v>
-      </c>
-      <c r="E9" s="6">
-        <v>0</v>
-      </c>
-      <c r="F9" s="6">
-        <v>0</v>
-      </c>
       <c r="G9" s="6">
         <v>0</v>
       </c>
@@ -998,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="J9" s="6">
-        <v>1599.6859999999999</v>
+        <v>0</v>
       </c>
       <c r="K9" s="6">
-        <v>799.84299999999996</v>
+        <v>0</v>
       </c>
       <c r="L9" s="6">
         <v>0</v>
@@ -1009,28 +1046,29 @@
       <c r="M9" s="6">
         <v>0</v>
       </c>
-      <c r="N9" s="7">
-        <v>0</v>
-      </c>
-      <c r="O9" s="7">
-        <v>0</v>
-      </c>
+      <c r="N9" s="6">
+        <v>0</v>
+      </c>
+      <c r="O9" s="6">
+        <v>0</v>
+      </c>
+      <c r="P9" s="4"/>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>27</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D10" s="5">
         <v>0</v>
       </c>
       <c r="E10" s="6">
-        <v>699.10500000000002</v>
+        <v>0</v>
       </c>
       <c r="F10" s="6">
         <v>0</v>
@@ -1045,10 +1083,10 @@
         <v>0</v>
       </c>
       <c r="J10" s="6">
-        <v>0</v>
+        <v>1599.6859999999999</v>
       </c>
       <c r="K10" s="6">
-        <v>0</v>
+        <v>799.84299999999996</v>
       </c>
       <c r="L10" s="6">
         <v>0</v>
@@ -1065,28 +1103,28 @@
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D11" s="5">
         <v>0</v>
       </c>
       <c r="E11" s="6">
-        <v>0</v>
+        <v>699.10500000000002</v>
       </c>
       <c r="F11" s="6">
-        <v>510.34665000000001</v>
+        <v>0</v>
       </c>
       <c r="G11" s="6">
         <v>0</v>
       </c>
       <c r="H11" s="6">
-        <v>163.04090000000002</v>
+        <v>0</v>
       </c>
       <c r="I11" s="6">
         <v>0</v>
@@ -1114,191 +1152,241 @@
       <c r="A12" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B12" t="s">
-        <v>23</v>
+      <c r="B12" s="1" t="s">
+        <v>22</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D12" s="5">
-        <v>35.058847499999999</v>
+        <v>0</v>
       </c>
       <c r="E12" s="6">
-        <v>43.280577025000007</v>
+        <v>0</v>
       </c>
       <c r="F12" s="6">
-        <v>51.368069475000006</v>
+        <v>510.34665000000001</v>
       </c>
       <c r="G12" s="6">
-        <v>56.493756987500014</v>
+        <v>0</v>
       </c>
       <c r="H12" s="6">
-        <v>55.611654274999992</v>
+        <v>163.04090000000002</v>
       </c>
       <c r="I12" s="6">
-        <v>56.91652052500001</v>
+        <v>0</v>
       </c>
       <c r="J12" s="6">
-        <v>63.990190350000013</v>
+        <v>0</v>
       </c>
       <c r="K12" s="6">
-        <v>50.678519424999998</v>
+        <v>0</v>
       </c>
       <c r="L12" s="6">
-        <v>37.898519387500009</v>
+        <v>0</v>
       </c>
       <c r="M12" s="6">
-        <v>37.857080775000007</v>
+        <v>0</v>
       </c>
       <c r="N12" s="7">
-        <v>32.31682215</v>
+        <v>0</v>
       </c>
       <c r="O12" s="7">
-        <v>46.149832274999994</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>24</v>
+        <v>29</v>
+      </c>
+      <c r="B13" t="s">
+        <v>23</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D13" s="5">
-        <v>36.575000000000003</v>
+        <v>35.058847499999999</v>
       </c>
       <c r="E13" s="6">
-        <v>36.575000000000003</v>
+        <v>43.280577025000007</v>
       </c>
       <c r="F13" s="6">
-        <v>36.575000000000003</v>
+        <v>51.368069475000006</v>
       </c>
       <c r="G13" s="6">
-        <v>36.575000000000003</v>
+        <v>56.493756987500014</v>
       </c>
       <c r="H13" s="6">
-        <v>36.575000000000003</v>
+        <v>55.611654274999992</v>
       </c>
       <c r="I13" s="6">
-        <v>36.575000000000003</v>
+        <v>56.91652052500001</v>
       </c>
       <c r="J13" s="6">
-        <v>36.575000000000003</v>
+        <v>63.990190350000013</v>
       </c>
       <c r="K13" s="6">
-        <v>36.575000000000003</v>
+        <v>50.678519424999998</v>
       </c>
       <c r="L13" s="6">
-        <v>36.575000000000003</v>
+        <v>37.898519387500009</v>
       </c>
       <c r="M13" s="6">
-        <v>36.575000000000003</v>
+        <v>37.857080775000007</v>
       </c>
       <c r="N13" s="7">
-        <v>36.575000000000003</v>
+        <v>32.31682215</v>
       </c>
       <c r="O13" s="7">
-        <v>36.575000000000003</v>
+        <v>46.149832274999994</v>
       </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D14" s="5">
-        <v>31.35</v>
+        <v>36.575000000000003</v>
       </c>
       <c r="E14" s="6">
-        <v>31.35</v>
+        <v>36.575000000000003</v>
       </c>
       <c r="F14" s="6">
-        <v>31.35</v>
+        <v>36.575000000000003</v>
       </c>
       <c r="G14" s="6">
-        <v>31.35</v>
+        <v>36.575000000000003</v>
       </c>
       <c r="H14" s="6">
-        <v>31.35</v>
+        <v>36.575000000000003</v>
       </c>
       <c r="I14" s="6">
-        <v>31.35</v>
+        <v>36.575000000000003</v>
       </c>
       <c r="J14" s="6">
-        <v>31.35</v>
+        <v>36.575000000000003</v>
       </c>
       <c r="K14" s="6">
-        <v>31.35</v>
+        <v>36.575000000000003</v>
       </c>
       <c r="L14" s="6">
-        <v>31.35</v>
+        <v>36.575000000000003</v>
       </c>
       <c r="M14" s="6">
-        <v>31.35</v>
+        <v>36.575000000000003</v>
       </c>
       <c r="N14" s="7">
-        <v>31.35</v>
+        <v>36.575000000000003</v>
       </c>
       <c r="O14" s="7">
-        <v>31.35</v>
+        <v>36.575000000000003</v>
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D15" s="5">
+        <v>31.35</v>
+      </c>
+      <c r="E15" s="6">
+        <v>31.35</v>
+      </c>
+      <c r="F15" s="6">
+        <v>31.35</v>
+      </c>
+      <c r="G15" s="6">
+        <v>31.35</v>
+      </c>
+      <c r="H15" s="6">
+        <v>31.35</v>
+      </c>
+      <c r="I15" s="6">
+        <v>31.35</v>
+      </c>
+      <c r="J15" s="6">
+        <v>31.35</v>
+      </c>
+      <c r="K15" s="6">
+        <v>31.35</v>
+      </c>
+      <c r="L15" s="6">
+        <v>31.35</v>
+      </c>
+      <c r="M15" s="6">
+        <v>31.35</v>
+      </c>
+      <c r="N15" s="7">
+        <v>31.35</v>
+      </c>
+      <c r="O15" s="7">
+        <v>31.35</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A16" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="B16" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="C16" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D15" s="5">
+      <c r="D16" s="5">
         <v>1096.6739322999997</v>
       </c>
-      <c r="E15" s="6">
+      <c r="E16" s="6">
         <v>817.91695954999989</v>
       </c>
-      <c r="F15" s="6">
+      <c r="F16" s="6">
         <v>2046.5947922000005</v>
       </c>
-      <c r="G15" s="6">
+      <c r="G16" s="6">
         <v>713.20505524999976</v>
       </c>
-      <c r="H15" s="6">
+      <c r="H16" s="6">
         <v>835.92150179999999</v>
       </c>
-      <c r="I15" s="6">
+      <c r="I16" s="6">
         <v>812.07111809999992</v>
       </c>
-      <c r="J15" s="6">
+      <c r="J16" s="6">
         <v>979.39609810000002</v>
       </c>
-      <c r="K15" s="6">
+      <c r="K16" s="6">
         <v>627.47923185000013</v>
       </c>
-      <c r="L15" s="6">
+      <c r="L16" s="6">
         <v>746.54498694999984</v>
       </c>
-      <c r="M15" s="6">
+      <c r="M16" s="6">
         <v>999.16518334999989</v>
       </c>
-      <c r="N15" s="7">
+      <c r="N16" s="7">
         <v>1045.7847295000004</v>
       </c>
-      <c r="O15" s="7">
+      <c r="O16" s="7">
         <v>1105.0784094000001</v>
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="C3">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>